--- a/02_ai-risk-framework-implementation-nist-ai-rmf/exercises/starter/risk_assessment.xlsx
+++ b/02_ai-risk-framework-implementation-nist-ai-rmf/exercises/starter/risk_assessment.xlsx
@@ -1008,12 +1008,12 @@
       </c>
       <c r="F5" s="13" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — score 1-5 reflecting how severe this risk's worst-case outcome would be for FinGuard (financial loss, customer harm, regulatory penalty); see the Scoring Rubric sheet for what each level means.]</t>
         </is>
       </c>
       <c r="G5" s="13" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — score 1-5 estimating how likely this risk is to materialize within ~12 months given the scenario context; see the Scoring Rubric sheet for level definitions.]</t>
         </is>
       </c>
       <c r="H5" s="12">
@@ -1026,22 +1026,22 @@
       </c>
       <c r="J5" s="13" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — name 2-3 specific controls that would reduce this risk's likelihood or impact (think monitoring, validation, governance, human-in-the-loop, redundancy); match them to the risk type.]</t>
         </is>
       </c>
       <c r="K5" s="13" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — assign Critical / High / Medium / Low based on the Risk Score band and business urgency; cross-check against the Scoring Rubric thresholds.]</t>
         </is>
       </c>
       <c r="L5" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — pick the current state of this mitigation: Open, In Progress, or Closed (most starter risks will be Open).]</t>
         </is>
       </c>
       <c r="M5" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — propose a realistic target completion date (e.g., "Q2 2026") or "TBD" if owner needs to scope first; align urgency with the Priority you assigned.]</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="F6" s="13" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — score 1-5 reflecting how severe this risk's worst-case outcome would be for FinGuard (financial loss, customer harm, regulatory penalty); see the Scoring Rubric sheet for what each level means.]</t>
         </is>
       </c>
       <c r="G6" s="13" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — score 1-5 estimating how likely this risk is to materialize within ~12 months given the scenario context; see the Scoring Rubric sheet for level definitions.]</t>
         </is>
       </c>
       <c r="H6" s="12">
@@ -1091,22 +1091,22 @@
       </c>
       <c r="J6" s="13" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — name 2-3 specific controls that would reduce this risk's likelihood or impact (think monitoring, validation, governance, human-in-the-loop, redundancy); match them to the risk type.]</t>
         </is>
       </c>
       <c r="K6" s="13" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — assign Critical / High / Medium / Low based on the Risk Score band and business urgency; cross-check against the Scoring Rubric thresholds.]</t>
         </is>
       </c>
       <c r="L6" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — pick the current state of this mitigation: Open, In Progress, or Closed (most starter risks will be Open).]</t>
         </is>
       </c>
       <c r="M6" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — propose a realistic target completion date (e.g., "Q2 2026") or "TBD" if owner needs to scope first; align urgency with the Priority you assigned.]</t>
         </is>
       </c>
     </row>
@@ -1138,12 +1138,12 @@
       </c>
       <c r="F7" s="13" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — score 1-5 reflecting how severe this risk's worst-case outcome would be for FinGuard (financial loss, customer harm, regulatory penalty); see the Scoring Rubric sheet for what each level means.]</t>
         </is>
       </c>
       <c r="G7" s="13" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — score 1-5 estimating how likely this risk is to materialize within ~12 months given the scenario context; see the Scoring Rubric sheet for level definitions.]</t>
         </is>
       </c>
       <c r="H7" s="12">
@@ -1156,22 +1156,22 @@
       </c>
       <c r="J7" s="13" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — name 2-3 specific controls that would reduce this risk's likelihood or impact (think monitoring, validation, governance, human-in-the-loop, redundancy); match them to the risk type.]</t>
         </is>
       </c>
       <c r="K7" s="13" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — assign Critical / High / Medium / Low based on the Risk Score band and business urgency; cross-check against the Scoring Rubric thresholds.]</t>
         </is>
       </c>
       <c r="L7" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — pick the current state of this mitigation: Open, In Progress, or Closed (most starter risks will be Open).]</t>
         </is>
       </c>
       <c r="M7" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — propose a realistic target completion date (e.g., "Q2 2026") or "TBD" if owner needs to scope first; align urgency with the Priority you assigned.]</t>
         </is>
       </c>
     </row>
@@ -1203,12 +1203,12 @@
       </c>
       <c r="F8" s="13" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — score 1-5 reflecting how severe this risk's worst-case outcome would be for FinGuard (financial loss, customer harm, regulatory penalty); see the Scoring Rubric sheet for what each level means.]</t>
         </is>
       </c>
       <c r="G8" s="13" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — score 1-5 estimating how likely this risk is to materialize within ~12 months given the scenario context; see the Scoring Rubric sheet for level definitions.]</t>
         </is>
       </c>
       <c r="H8" s="12">
@@ -1221,22 +1221,22 @@
       </c>
       <c r="J8" s="13" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — name 2-3 specific controls that would reduce this risk's likelihood or impact (think monitoring, validation, governance, human-in-the-loop, redundancy); match them to the risk type.]</t>
         </is>
       </c>
       <c r="K8" s="13" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — assign Critical / High / Medium / Low based on the Risk Score band and business urgency; cross-check against the Scoring Rubric thresholds.]</t>
         </is>
       </c>
       <c r="L8" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — pick the current state of this mitigation: Open, In Progress, or Closed (most starter risks will be Open).]</t>
         </is>
       </c>
       <c r="M8" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — propose a realistic target completion date (e.g., "Q2 2026") or "TBD" if owner needs to scope first; align urgency with the Priority you assigned.]</t>
         </is>
       </c>
     </row>
@@ -1268,12 +1268,12 @@
       </c>
       <c r="F9" s="13" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — score 1-5 reflecting how severe this risk's worst-case outcome would be for FinGuard (financial loss, customer harm, regulatory penalty); see the Scoring Rubric sheet for what each level means.]</t>
         </is>
       </c>
       <c r="G9" s="13" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — score 1-5 estimating how likely this risk is to materialize within ~12 months given the scenario context; see the Scoring Rubric sheet for level definitions.]</t>
         </is>
       </c>
       <c r="H9" s="12">
@@ -1286,22 +1286,22 @@
       </c>
       <c r="J9" s="13" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — name 2-3 specific controls that would reduce this risk's likelihood or impact (think monitoring, validation, governance, human-in-the-loop, redundancy); match them to the risk type.]</t>
         </is>
       </c>
       <c r="K9" s="13" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — assign Critical / High / Medium / Low based on the Risk Score band and business urgency; cross-check against the Scoring Rubric thresholds.]</t>
         </is>
       </c>
       <c r="L9" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — pick the current state of this mitigation: Open, In Progress, or Closed (most starter risks will be Open).]</t>
         </is>
       </c>
       <c r="M9" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — propose a realistic target completion date (e.g., "Q2 2026") or "TBD" if owner needs to scope first; align urgency with the Priority you assigned.]</t>
         </is>
       </c>
     </row>
@@ -1333,12 +1333,12 @@
       </c>
       <c r="F10" s="13" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — score 1-5 reflecting how severe this risk's worst-case outcome would be for FinGuard (financial loss, customer harm, regulatory penalty); see the Scoring Rubric sheet for what each level means.]</t>
         </is>
       </c>
       <c r="G10" s="13" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — score 1-5 estimating how likely this risk is to materialize within ~12 months given the scenario context; see the Scoring Rubric sheet for level definitions.]</t>
         </is>
       </c>
       <c r="H10" s="12">
@@ -1351,22 +1351,22 @@
       </c>
       <c r="J10" s="13" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — name 2-3 specific controls that would reduce this risk's likelihood or impact (think monitoring, validation, governance, human-in-the-loop, redundancy); match them to the risk type.]</t>
         </is>
       </c>
       <c r="K10" s="13" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — assign Critical / High / Medium / Low based on the Risk Score band and business urgency; cross-check against the Scoring Rubric thresholds.]</t>
         </is>
       </c>
       <c r="L10" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — pick the current state of this mitigation: Open, In Progress, or Closed (most starter risks will be Open).]</t>
         </is>
       </c>
       <c r="M10" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — propose a realistic target completion date (e.g., "Q2 2026") or "TBD" if owner needs to scope first; align urgency with the Priority you assigned.]</t>
         </is>
       </c>
     </row>
@@ -1398,12 +1398,12 @@
       </c>
       <c r="F11" s="13" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — score 1-5 reflecting how severe this risk's worst-case outcome would be for FinGuard (financial loss, customer harm, regulatory penalty); see the Scoring Rubric sheet for what each level means.]</t>
         </is>
       </c>
       <c r="G11" s="13" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — score 1-5 estimating how likely this risk is to materialize within ~12 months given the scenario context; see the Scoring Rubric sheet for level definitions.]</t>
         </is>
       </c>
       <c r="H11" s="12">
@@ -1416,22 +1416,22 @@
       </c>
       <c r="J11" s="13" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — name 2-3 specific controls that would reduce this risk's likelihood or impact (think monitoring, validation, governance, human-in-the-loop, redundancy); match them to the risk type.]</t>
         </is>
       </c>
       <c r="K11" s="13" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — assign Critical / High / Medium / Low based on the Risk Score band and business urgency; cross-check against the Scoring Rubric thresholds.]</t>
         </is>
       </c>
       <c r="L11" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — pick the current state of this mitigation: Open, In Progress, or Closed (most starter risks will be Open).]</t>
         </is>
       </c>
       <c r="M11" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — propose a realistic target completion date (e.g., "Q2 2026") or "TBD" if owner needs to scope first; align urgency with the Priority you assigned.]</t>
         </is>
       </c>
     </row>
@@ -1484,22 +1484,22 @@
       </c>
       <c r="J12" s="13" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — name 2-3 specific controls that would reduce this risk's likelihood or impact (think monitoring, validation, governance, human-in-the-loop, redundancy); match them to the risk type.]</t>
         </is>
       </c>
       <c r="K12" s="13" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — assign Critical / High / Medium / Low based on the Risk Score band and business urgency; cross-check against the Scoring Rubric thresholds.]</t>
         </is>
       </c>
       <c r="L12" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — pick the current state of this mitigation: Open, In Progress, or Closed (most starter risks will be Open).]</t>
         </is>
       </c>
       <c r="M12" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — propose a realistic target completion date (e.g., "Q2 2026") or "TBD" if owner needs to scope first; align urgency with the Priority you assigned.]</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="F13" s="13" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — score 1-5 reflecting how severe this risk's worst-case outcome would be for FinGuard (financial loss, customer harm, regulatory penalty); see the Scoring Rubric sheet for what each level means.]</t>
         </is>
       </c>
       <c r="G13" s="13" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — score 1-5 estimating how likely this risk is to materialize within ~12 months given the scenario context; see the Scoring Rubric sheet for level definitions.]</t>
         </is>
       </c>
       <c r="H13" s="12">
@@ -1549,22 +1549,22 @@
       </c>
       <c r="J13" s="13" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — name 2-3 specific controls that would reduce this risk's likelihood or impact (think monitoring, validation, governance, human-in-the-loop, redundancy); match them to the risk type.]</t>
         </is>
       </c>
       <c r="K13" s="13" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — assign Critical / High / Medium / Low based on the Risk Score band and business urgency; cross-check against the Scoring Rubric thresholds.]</t>
         </is>
       </c>
       <c r="L13" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — pick the current state of this mitigation: Open, In Progress, or Closed (most starter risks will be Open).]</t>
         </is>
       </c>
       <c r="M13" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — propose a realistic target completion date (e.g., "Q2 2026") or "TBD" if owner needs to scope first; align urgency with the Priority you assigned.]</t>
         </is>
       </c>
     </row>
@@ -1596,12 +1596,12 @@
       </c>
       <c r="F14" s="13" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — score 1-5 reflecting how severe this risk's worst-case outcome would be for FinGuard (financial loss, customer harm, regulatory penalty); see the Scoring Rubric sheet for what each level means.]</t>
         </is>
       </c>
       <c r="G14" s="13" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — score 1-5 estimating how likely this risk is to materialize within ~12 months given the scenario context; see the Scoring Rubric sheet for level definitions.]</t>
         </is>
       </c>
       <c r="H14" s="12">
@@ -1614,22 +1614,22 @@
       </c>
       <c r="J14" s="13" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — name 2-3 specific controls that would reduce this risk's likelihood or impact (think monitoring, validation, governance, human-in-the-loop, redundancy); match them to the risk type.]</t>
         </is>
       </c>
       <c r="K14" s="13" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — assign Critical / High / Medium / Low based on the Risk Score band and business urgency; cross-check against the Scoring Rubric thresholds.]</t>
         </is>
       </c>
       <c r="L14" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — pick the current state of this mitigation: Open, In Progress, or Closed (most starter risks will be Open).]</t>
         </is>
       </c>
       <c r="M14" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — propose a realistic target completion date (e.g., "Q2 2026") or "TBD" if owner needs to scope first; align urgency with the Priority you assigned.]</t>
         </is>
       </c>
     </row>
@@ -1682,22 +1682,22 @@
       </c>
       <c r="J15" s="13" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — name 2-3 specific controls that would reduce this risk's likelihood or impact (think monitoring, validation, governance, human-in-the-loop, redundancy); match them to the risk type.]</t>
         </is>
       </c>
       <c r="K15" s="13" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — assign Critical / High / Medium / Low based on the Risk Score band and business urgency; cross-check against the Scoring Rubric thresholds.]</t>
         </is>
       </c>
       <c r="L15" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — pick the current state of this mitigation: Open, In Progress, or Closed (most starter risks will be Open).]</t>
         </is>
       </c>
       <c r="M15" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — propose a realistic target completion date (e.g., "Q2 2026") or "TBD" if owner needs to scope first; align urgency with the Priority you assigned.]</t>
         </is>
       </c>
     </row>
@@ -1729,12 +1729,12 @@
       </c>
       <c r="F16" s="13" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — score 1-5 reflecting how severe this risk's worst-case outcome would be for FinGuard (financial loss, customer harm, regulatory penalty); see the Scoring Rubric sheet for what each level means.]</t>
         </is>
       </c>
       <c r="G16" s="13" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — score 1-5 estimating how likely this risk is to materialize within ~12 months given the scenario context; see the Scoring Rubric sheet for level definitions.]</t>
         </is>
       </c>
       <c r="H16" s="12">
@@ -1747,43 +1747,217 @@
       </c>
       <c r="J16" s="13" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — name 2-3 specific controls that would reduce this risk's likelihood or impact (think monitoring, validation, governance, human-in-the-loop, redundancy); match them to the risk type.]</t>
         </is>
       </c>
       <c r="K16" s="13" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — assign Critical / High / Medium / Low based on the Risk Score band and business urgency; cross-check against the Scoring Rubric thresholds.]</t>
         </is>
       </c>
       <c r="L16" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — pick the current state of this mitigation: Open, In Progress, or Closed (most starter risks will be Open).]</t>
         </is>
       </c>
       <c r="M16" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — propose a realistic target completion date (e.g., "Q2 2026") or "TBD" if owner needs to scope first; align urgency with the Priority you assigned.]</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="12" t="inlineStr">
         <is>
           <t>R016</t>
         </is>
       </c>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>Measure</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>Technical</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="inlineStr">
+        <is>
+          <t>GENAI-SPECIFIC: Hallucinated fraud explanations - System generates plausible but fabricated reasoning when flagging transactions, misleading analysts</t>
+        </is>
+      </c>
+      <c r="E17" s="12" t="inlineStr">
+        <is>
+          <t>Data Science Lead</t>
+        </is>
+      </c>
+      <c r="F17" s="13" t="inlineStr">
+        <is>
+          <t>[Your response here — score 1-5 reflecting how severe this risk's worst-case outcome would be for FinGuard (financial loss, customer harm, regulatory penalty); see the Scoring Rubric sheet for what each level means.]</t>
+        </is>
+      </c>
+      <c r="G17" s="13" t="inlineStr">
+        <is>
+          <t>[Your response here — score 1-5 estimating how likely this risk is to materialize within ~12 months given the scenario context; see the Scoring Rubric sheet for level definitions.]</t>
+        </is>
+      </c>
+      <c r="H17" s="12">
+        <f>IF(F17="","",F17*G17)</f>
+        <v/>
+      </c>
+      <c r="I17" s="12">
+        <f>IF(F17="","",IF(H17&gt;=15,"Critical",IF(H17&gt;=10,"High",IF(H17&gt;=5,"Medium","Low"))))</f>
+        <v/>
+      </c>
+      <c r="J17" s="13" t="inlineStr">
+        <is>
+          <t>[Your response here — name 2-3 specific controls that would reduce this risk's likelihood or impact (think monitoring, validation, governance, human-in-the-loop, redundancy); match them to the risk type.]</t>
+        </is>
+      </c>
+      <c r="K17" s="13" t="inlineStr">
+        <is>
+          <t>[Your response here — assign Critical / High / Medium / Low based on the Risk Score band and business urgency; cross-check against the Scoring Rubric thresholds.]</t>
+        </is>
+      </c>
+      <c r="L17" s="12" t="inlineStr">
+        <is>
+          <t>[Your response here — pick the current state of this mitigation: Open, In Progress, or Closed (most starter risks will be Open).]</t>
+        </is>
+      </c>
+      <c r="M17" s="12" t="inlineStr">
+        <is>
+          <t>[Your response here — propose a realistic target completion date (e.g., "Q2 2026") or "TBD" if owner needs to scope first; align urgency with the Priority you assigned.]</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="12" t="inlineStr">
         <is>
           <t>R017</t>
         </is>
       </c>
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>Manage</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>Technical</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="inlineStr">
+        <is>
+          <t>GENAI-SPECIFIC: Prompt injection vulnerabilities - Adversarial prompts manipulate fraud detection outputs, causing false positives or false negatives</t>
+        </is>
+      </c>
+      <c r="E18" s="12" t="inlineStr">
+        <is>
+          <t>ML Security Engineer</t>
+        </is>
+      </c>
+      <c r="F18" s="13" t="inlineStr">
+        <is>
+          <t>[Your response here — score 1-5 reflecting how severe this risk's worst-case outcome would be for FinGuard (financial loss, customer harm, regulatory penalty); see the Scoring Rubric sheet for what each level means.]</t>
+        </is>
+      </c>
+      <c r="G18" s="13" t="inlineStr">
+        <is>
+          <t>[Your response here — score 1-5 estimating how likely this risk is to materialize within ~12 months given the scenario context; see the Scoring Rubric sheet for level definitions.]</t>
+        </is>
+      </c>
+      <c r="H18" s="12">
+        <f>IF(F18="","",F18*G18)</f>
+        <v/>
+      </c>
+      <c r="I18" s="12">
+        <f>IF(F18="","",IF(H18&gt;=15,"Critical",IF(H18&gt;=10,"High",IF(H18&gt;=5,"Medium","Low"))))</f>
+        <v/>
+      </c>
+      <c r="J18" s="13" t="inlineStr">
+        <is>
+          <t>[Your response here — name 2-3 specific controls that would reduce this risk's likelihood or impact (think monitoring, validation, governance, human-in-the-loop, redundancy); match them to the risk type.]</t>
+        </is>
+      </c>
+      <c r="K18" s="13" t="inlineStr">
+        <is>
+          <t>[Your response here — assign Critical / High / Medium / Low based on the Risk Score band and business urgency; cross-check against the Scoring Rubric thresholds.]</t>
+        </is>
+      </c>
+      <c r="L18" s="12" t="inlineStr">
+        <is>
+          <t>[Your response here — pick the current state of this mitigation: Open, In Progress, or Closed (most starter risks will be Open).]</t>
+        </is>
+      </c>
+      <c r="M18" s="12" t="inlineStr">
+        <is>
+          <t>[Your response here — propose a realistic target completion date (e.g., "Q2 2026") or "TBD" if owner needs to scope first; align urgency with the Priority you assigned.]</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="12" t="inlineStr">
         <is>
           <t>R018</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t>Govern</t>
+        </is>
+      </c>
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>Technical</t>
+        </is>
+      </c>
+      <c r="D19" s="12" t="inlineStr">
+        <is>
+          <t>GENAI-SPECIFIC: Training data poisoning - Contaminated training data causes systematic misclassifications in fraud detection model</t>
+        </is>
+      </c>
+      <c r="E19" s="12" t="inlineStr">
+        <is>
+          <t>Data Science Lead</t>
+        </is>
+      </c>
+      <c r="F19" s="13" t="inlineStr">
+        <is>
+          <t>[Your response here — score 1-5 reflecting how severe this risk's worst-case outcome would be for FinGuard (financial loss, customer harm, regulatory penalty); see the Scoring Rubric sheet for what each level means.]</t>
+        </is>
+      </c>
+      <c r="G19" s="13" t="inlineStr">
+        <is>
+          <t>[Your response here — score 1-5 estimating how likely this risk is to materialize within ~12 months given the scenario context; see the Scoring Rubric sheet for level definitions.]</t>
+        </is>
+      </c>
+      <c r="H19" s="12">
+        <f>IF(F19="","",F19*G19)</f>
+        <v/>
+      </c>
+      <c r="I19" s="12">
+        <f>IF(F19="","",IF(H19&gt;=15,"Critical",IF(H19&gt;=10,"High",IF(H19&gt;=5,"Medium","Low"))))</f>
+        <v/>
+      </c>
+      <c r="J19" s="13" t="inlineStr">
+        <is>
+          <t>[Your response here — name 2-3 specific controls that would reduce this risk's likelihood or impact (think monitoring, validation, governance, human-in-the-loop, redundancy); match them to the risk type.]</t>
+        </is>
+      </c>
+      <c r="K19" s="13" t="inlineStr">
+        <is>
+          <t>[Your response here — assign Critical / High / Medium / Low based on the Risk Score band and business urgency; cross-check against the Scoring Rubric thresholds.]</t>
+        </is>
+      </c>
+      <c r="L19" s="12" t="inlineStr">
+        <is>
+          <t>[Your response here — pick the current state of this mitigation: Open, In Progress, or Closed (most starter risks will be Open).]</t>
+        </is>
+      </c>
+      <c r="M19" s="12" t="inlineStr">
+        <is>
+          <t>[Your response here — propose a realistic target completion date (e.g., "Q2 2026") or "TBD" if owner needs to scope first; align urgency with the Priority you assigned.]</t>
         </is>
       </c>
     </row>
@@ -1987,7 +2161,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -2015,7 +2189,7 @@
         </is>
       </c>
       <c r="B4">
-        <f>COUNTA('Risk Register'!A2:A16)</f>
+        <f>COUNTA('Risk Register'!A2:A19)</f>
         <v/>
       </c>
     </row>
@@ -2026,7 +2200,7 @@
         </is>
       </c>
       <c r="B5">
-        <f>COUNTIF('Risk Register'!I2:I16,"Critical")</f>
+        <f>COUNTIF('Risk Register'!I2:I19,"Critical")</f>
         <v/>
       </c>
     </row>
@@ -2037,7 +2211,7 @@
         </is>
       </c>
       <c r="B6">
-        <f>COUNTIF('Risk Register'!I2:I16,"High")</f>
+        <f>COUNTIF('Risk Register'!I2:I19,"High")</f>
         <v/>
       </c>
     </row>
@@ -2048,7 +2222,7 @@
         </is>
       </c>
       <c r="B7">
-        <f>COUNTIF('Risk Register'!I2:I16,"Medium")</f>
+        <f>COUNTIF('Risk Register'!I2:I19,"Medium")</f>
         <v/>
       </c>
     </row>
@@ -2059,7 +2233,7 @@
         </is>
       </c>
       <c r="B8">
-        <f>COUNTIF('Risk Register'!I2:I16,"Low")</f>
+        <f>COUNTIF('Risk Register'!I2:I19,"Low")</f>
         <v/>
       </c>
     </row>
@@ -2077,7 +2251,7 @@
         </is>
       </c>
       <c r="B11">
-        <f>COUNTIF('Risk Register'!C2:C16,"Technical")</f>
+        <f>COUNTIF('Risk Register'!C2:C19,"Technical")</f>
         <v/>
       </c>
     </row>
@@ -2088,7 +2262,7 @@
         </is>
       </c>
       <c r="B12">
-        <f>COUNTIF('Risk Register'!C2:C16,"Ethical")</f>
+        <f>COUNTIF('Risk Register'!C2:C19,"Ethical")</f>
         <v/>
       </c>
     </row>
@@ -2099,7 +2273,7 @@
         </is>
       </c>
       <c r="B13">
-        <f>COUNTIF('Risk Register'!C2:C16,"Legal")</f>
+        <f>COUNTIF('Risk Register'!C2:C19,"Legal")</f>
         <v/>
       </c>
     </row>
@@ -2110,7 +2284,7 @@
         </is>
       </c>
       <c r="B14">
-        <f>COUNTIF('Risk Register'!C2:C16,"Operational")</f>
+        <f>COUNTIF('Risk Register'!C2:C19,"Operational")</f>
         <v/>
       </c>
     </row>
@@ -2128,7 +2302,7 @@
         </is>
       </c>
       <c r="B17">
-        <f>COUNTIF('Risk Register'!B2:B16,"Govern")</f>
+        <f>COUNTIF('Risk Register'!B2:B19,"Govern")</f>
         <v/>
       </c>
     </row>
@@ -2139,7 +2313,7 @@
         </is>
       </c>
       <c r="B18">
-        <f>COUNTIF('Risk Register'!B2:B16,"Map")</f>
+        <f>COUNTIF('Risk Register'!B2:B19,"Map")</f>
         <v/>
       </c>
     </row>
@@ -2150,7 +2324,7 @@
         </is>
       </c>
       <c r="B19">
-        <f>COUNTIF('Risk Register'!B2:B16,"Measure")</f>
+        <f>COUNTIF('Risk Register'!B2:B19,"Measure")</f>
         <v/>
       </c>
     </row>
@@ -2161,28 +2335,77 @@
         </is>
       </c>
       <c r="B20">
-        <f>COUNTIF('Risk Register'!B2:B16,"Manage")</f>
+        <f>COUNTIF('Risk Register'!B2:B19,"Manage")</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="16" t="inlineStr">
         <is>
-          <t>KEY FINDINGS</t>
+          <t>TOP 5 PRIORITY RISKS</t>
         </is>
       </c>
     </row>
     <row r="23" ht="30" customHeight="1">
       <c r="A23" s="17" t="inlineStr">
         <is>
-          <t>Hint: Summarize the overall risk posture — what is the biggest concern?</t>
+          <t>1. [Your response here — Risk #1: list Risk ID, short name, Risk Level, and Impact x Likelihood for the highest-scored risk in your register.]</t>
         </is>
       </c>
     </row>
     <row r="24" ht="30" customHeight="1">
       <c r="A24" s="17" t="inlineStr">
         <is>
-          <t>Hint: What patterns do you see across categories? Any clusters of risk?</t>
+          <t>2. [Your response here — Risk #2: same format as above, next-highest scored risk; break ties by business impact.]</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>3. [Your response here — Risk #3: same format; consider both Critical risks and any High risks with strategic significance.]</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>4. [Your response here — Risk #4: same format; remember GenAI-specific and legal risks may rank here.]</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>5. [Your response here — Risk #5: same format; round out the top 5 with the next priority risk an executive should track.]</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="16" t="inlineStr">
+        <is>
+          <t>KEY FINDINGS</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>[Your response here — one sentence summarizing FinGuard's overall risk posture: which risk category (technical, ethical, legal, operational) dominates and why it matters to leadership?]</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>[Your response here — call out patterns or clusters across NIST AI RMF functions or risk categories (e.g., concentration in Measure, multiple bias-related risks); reference the counts in B5:B20.]</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>[Your response here — one sentence on legal/regulatory exposure for executives, naming the specific regimes at play (e.g., GDPR Article 22, EU AI Act high-risk obligations).]</t>
         </is>
       </c>
     </row>

--- a/02_ai-risk-framework-implementation-nist-ai-rmf/exercises/starter/risk_assessment.xlsx
+++ b/02_ai-risk-framework-implementation-nist-ai-rmf/exercises/starter/risk_assessment.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
+  <fileVersion appName="Calc" lowestEdited="4"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
@@ -23,8 +23,66 @@
 </workbook>
 </file>
 
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <authors>
+    <author>Solution</author>
+  </authors>
+  <commentList>
+    <comment ref="F12" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Impact=2 (Low): Losing a data feed temporarily degrades detection capability. Impact is manageable given data redundancy and alternative sources.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F15" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Impact=2 (Low): Non-compliance creates minor regulatory exposure, mostly administrative in nature.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G12" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Likelihood=2 (Unlikely): Established vendors rarely fail completely. With proper vendor SLAs, failure is unlikely.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G15" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Likelihood=2 (Unlikely): Data retention violations are not a priority for most regulators.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="166">
   <si>
     <t xml:space="preserve">FinGuard AI - FraudShield Risk Assessment</t>
   </si>
@@ -299,18 +357,6 @@
     <t xml:space="preserve">Vendor Manager</t>
   </si>
   <si>
-    <t xml:space="preserve">"2"
-Reasoning: Impact=2 (Low): Losing a data feed temporarily degrades detection capability. Impact is manageable given data redundancy and alternative sources.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"2"
-Reasoning: Likelihood=2 (Unlikely): Established vendors rarely fail completely. With proper vendor SLAs, failure is unlikely.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"Low"
-Reasoning: Score 4 (&lt;5) = Low. Standard vendor risk management with acceptable mitigation strategies.</t>
-  </si>
-  <si>
     <t xml:space="preserve">R012</t>
   </si>
   <si>
@@ -333,18 +379,6 @@
   </si>
   <si>
     <t xml:space="preserve">Data Protection Officer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"2"
-Reasoning: Impact=2 (Low): Non-compliance creates minor regulatory exposure, mostly administrative in nature.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"2"
-Reasoning: Likelihood=2 (Unlikely): Data retention violations are not a priority for most regulators.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"Low"
-Reasoning: Score 4 (&lt;5) = Low. Data retention is important compliance housekeeping but lower risk tier.</t>
   </si>
   <si>
     <t xml:space="preserve">R015</t>
@@ -555,7 +589,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -608,6 +642,11 @@
       <name val="Cambria"/>
       <family val="0"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b val="true"/>
@@ -690,88 +729,84 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -855,34 +890,34 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -1028,7 +1063,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B28"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="120"/>
   </cols>
@@ -1038,130 +1073,130 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3"/>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3"/>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="3"/>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="3"/>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B24" s="7" t="s">
+      <c r="B24" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="8" t="s">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="B25" s="7" t="s">
+      <c r="B25" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="9" t="s">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="B26" s="7" t="s">
+      <c r="B26" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="10" t="s">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="B27" s="7" t="s">
+      <c r="B27" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="11" t="s">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="B28" s="7" t="s">
+      <c r="B28" s="1" t="s">
         <v>25</v>
       </c>
     </row>
@@ -1182,7 +1217,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:M19"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="14"/>
@@ -1198,813 +1233,817 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="I1" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="J1" s="12" t="s">
+      <c r="J1" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="K1" s="12" t="s">
+      <c r="K1" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="L1" s="12" t="s">
+      <c r="L1" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="M1" s="12" t="s">
+      <c r="M1" s="11" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="13" t="s">
+    <row r="2" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="D2" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="E2" s="13" t="s">
+      <c r="E2" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="F2" s="13" t="n">
+      <c r="F2" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="G2" s="13" t="n">
+      <c r="G2" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="H2" s="13" t="n">
+      <c r="H2" s="12" t="n">
         <f aca="false">F2*G2</f>
         <v>16</v>
       </c>
-      <c r="I2" s="13" t="str">
+      <c r="I2" s="12" t="str">
         <f aca="false">IF(H2&gt;=15,"Critical",IF(H2&gt;=10,"High",IF(H2&gt;=5,"Medium","Low")))</f>
         <v>Critical</v>
       </c>
-      <c r="J2" s="13" t="s">
+      <c r="J2" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="K2" s="13" t="s">
+      <c r="K2" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="L2" s="13" t="s">
+      <c r="L2" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="M2" s="13" t="s">
+      <c r="M2" s="12" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="13" t="s">
+    <row r="3" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="E3" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="F3" s="13" t="n">
+      <c r="F3" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="G3" s="13" t="n">
+      <c r="G3" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="H3" s="13" t="n">
+      <c r="H3" s="12" t="n">
         <f aca="false">F3*G3</f>
         <v>20</v>
       </c>
-      <c r="I3" s="13" t="str">
+      <c r="I3" s="12" t="str">
         <f aca="false">IF(H3&gt;=15,"Critical",IF(H3&gt;=10,"High",IF(H3&gt;=5,"Medium","Low")))</f>
         <v>Critical</v>
       </c>
-      <c r="J3" s="13" t="s">
+      <c r="J3" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="K3" s="13" t="s">
+      <c r="K3" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="L3" s="13" t="s">
+      <c r="L3" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="M3" s="13" t="s">
+      <c r="M3" s="12" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="13" t="s">
+    <row r="4" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="C4" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="D4" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="E4" s="13" t="s">
+      <c r="E4" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="F4" s="13" t="n">
+      <c r="F4" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="G4" s="13" t="n">
+      <c r="G4" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="H4" s="13" t="n">
+      <c r="H4" s="12" t="n">
         <f aca="false">F4*G4</f>
         <v>15</v>
       </c>
-      <c r="I4" s="13" t="str">
+      <c r="I4" s="12" t="str">
         <f aca="false">IF(H4&gt;=15,"Critical",IF(H4&gt;=10,"High",IF(H4&gt;=5,"Medium","Low")))</f>
         <v>Critical</v>
       </c>
-      <c r="J4" s="13" t="s">
+      <c r="J4" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="K4" s="13" t="s">
+      <c r="K4" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="L4" s="13" t="s">
+      <c r="L4" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="M4" s="13" t="s">
+      <c r="M4" s="12" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="337.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="14" t="s">
+    <row r="5" customFormat="false" ht="336.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="D5" s="14" t="s">
+      <c r="D5" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="E5" s="14" t="s">
+      <c r="E5" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="F5" s="15" t="s">
+      <c r="F5" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="G5" s="15" t="s">
+      <c r="G5" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="H5" s="14" t="e">
+      <c r="H5" s="13" t="e">
         <f aca="false">IF(F5="","",F5*G5)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="I5" s="14" t="e">
+      <c r="I5" s="13" t="e">
         <f aca="false">IF(F5="","",IF(H5&gt;=15,"Critical",IF(H5&gt;=10,"High",IF(H5&gt;=5,"Medium","Low"))))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J5" s="15" t="s">
+      <c r="J5" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="K5" s="15" t="s">
+      <c r="K5" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="L5" s="14" t="s">
+      <c r="L5" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="M5" s="14" t="s">
+      <c r="M5" s="13" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="337.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="14" t="s">
+    <row r="6" customFormat="false" ht="336.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C6" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="D6" s="14" t="s">
+      <c r="D6" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="E6" s="14" t="s">
+      <c r="E6" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="F6" s="15" t="s">
+      <c r="F6" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="G6" s="15" t="s">
+      <c r="G6" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="H6" s="14" t="e">
+      <c r="H6" s="13" t="e">
         <f aca="false">IF(F6="","",F6*G6)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="I6" s="14" t="e">
+      <c r="I6" s="13" t="e">
         <f aca="false">IF(F6="","",IF(H6&gt;=15,"Critical",IF(H6&gt;=10,"High",IF(H6&gt;=5,"Medium","Low"))))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J6" s="15" t="s">
+      <c r="J6" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="K6" s="15" t="s">
+      <c r="K6" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="L6" s="14" t="s">
+      <c r="L6" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="M6" s="14" t="s">
+      <c r="M6" s="13" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="337.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="14" t="s">
+    <row r="7" customFormat="false" ht="336.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="B7" s="14" t="s">
+      <c r="B7" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="C7" s="14" t="s">
+      <c r="C7" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="D7" s="14" t="s">
+      <c r="D7" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="E7" s="14" t="s">
+      <c r="E7" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="F7" s="15" t="s">
+      <c r="F7" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="G7" s="15" t="s">
+      <c r="G7" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="H7" s="14" t="e">
+      <c r="H7" s="13" t="e">
         <f aca="false">IF(F7="","",F7*G7)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="I7" s="14" t="e">
+      <c r="I7" s="13" t="e">
         <f aca="false">IF(F7="","",IF(H7&gt;=15,"Critical",IF(H7&gt;=10,"High",IF(H7&gt;=5,"Medium","Low"))))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J7" s="15" t="s">
+      <c r="J7" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="K7" s="15" t="s">
+      <c r="K7" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="L7" s="14" t="s">
+      <c r="L7" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="M7" s="14" t="s">
+      <c r="M7" s="13" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="337.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="14" t="s">
+    <row r="8" customFormat="false" ht="336.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="B8" s="14" t="s">
+      <c r="B8" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="C8" s="14" t="s">
+      <c r="C8" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="D8" s="14" t="s">
+      <c r="D8" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="E8" s="14" t="s">
+      <c r="E8" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="F8" s="15" t="s">
+      <c r="F8" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="G8" s="15" t="s">
+      <c r="G8" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="H8" s="14" t="e">
+      <c r="H8" s="13" t="e">
         <f aca="false">IF(F8="","",F8*G8)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="I8" s="14" t="e">
+      <c r="I8" s="13" t="e">
         <f aca="false">IF(F8="","",IF(H8&gt;=15,"Critical",IF(H8&gt;=10,"High",IF(H8&gt;=5,"Medium","Low"))))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J8" s="15" t="s">
+      <c r="J8" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="K8" s="15" t="s">
+      <c r="K8" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="L8" s="14" t="s">
+      <c r="L8" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="M8" s="14" t="s">
+      <c r="M8" s="13" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="337.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="14" t="s">
+    <row r="9" customFormat="false" ht="336.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="B9" s="14" t="s">
+      <c r="B9" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="C9" s="14" t="s">
+      <c r="C9" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="D9" s="14" t="s">
+      <c r="D9" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="E9" s="14" t="s">
+      <c r="E9" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="F9" s="15" t="s">
+      <c r="F9" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="G9" s="15" t="s">
+      <c r="G9" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="H9" s="14" t="e">
+      <c r="H9" s="13" t="e">
         <f aca="false">IF(F9="","",F9*G9)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="I9" s="14" t="e">
+      <c r="I9" s="13" t="e">
         <f aca="false">IF(F9="","",IF(H9&gt;=15,"Critical",IF(H9&gt;=10,"High",IF(H9&gt;=5,"Medium","Low"))))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J9" s="15" t="s">
+      <c r="J9" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="K9" s="15" t="s">
+      <c r="K9" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="L9" s="14" t="s">
+      <c r="L9" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="M9" s="14" t="s">
+      <c r="M9" s="13" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="337.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="14" t="s">
+    <row r="10" customFormat="false" ht="336.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="B10" s="14" t="s">
+      <c r="B10" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="C10" s="14" t="s">
+      <c r="C10" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="D10" s="14" t="s">
+      <c r="D10" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="E10" s="14" t="s">
+      <c r="E10" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="F10" s="15" t="s">
+      <c r="F10" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="G10" s="15" t="s">
+      <c r="G10" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="H10" s="14" t="e">
+      <c r="H10" s="13" t="e">
         <f aca="false">IF(F10="","",F10*G10)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="I10" s="14" t="e">
+      <c r="I10" s="13" t="e">
         <f aca="false">IF(F10="","",IF(H10&gt;=15,"Critical",IF(H10&gt;=10,"High",IF(H10&gt;=5,"Medium","Low"))))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J10" s="15" t="s">
+      <c r="J10" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="K10" s="15" t="s">
+      <c r="K10" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="L10" s="14" t="s">
+      <c r="L10" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="M10" s="14" t="s">
+      <c r="M10" s="13" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="337.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="14" t="s">
+    <row r="11" customFormat="false" ht="336.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="B11" s="14" t="s">
+      <c r="B11" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="C11" s="14" t="s">
+      <c r="C11" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="D11" s="14" t="s">
+      <c r="D11" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="E11" s="14" t="s">
+      <c r="E11" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="F11" s="15" t="s">
+      <c r="F11" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="G11" s="15" t="s">
+      <c r="G11" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="H11" s="14" t="e">
+      <c r="H11" s="13" t="e">
         <f aca="false">IF(F11="","",F11*G11)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="I11" s="14" t="e">
+      <c r="I11" s="13" t="e">
         <f aca="false">IF(F11="","",IF(H11&gt;=15,"Critical",IF(H11&gt;=10,"High",IF(H11&gt;=5,"Medium","Low"))))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J11" s="15" t="s">
+      <c r="J11" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="K11" s="15" t="s">
+      <c r="K11" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="L11" s="14" t="s">
+      <c r="L11" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="M11" s="14" t="s">
+      <c r="M11" s="13" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="270.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="14" t="s">
+    <row r="12" customFormat="false" ht="270" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="B12" s="14" t="s">
+      <c r="B12" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="C12" s="14" t="s">
+      <c r="C12" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="D12" s="14" t="s">
+      <c r="D12" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="E12" s="14" t="s">
+      <c r="E12" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="F12" s="15" t="s">
+      <c r="F12" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G12" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="H12" s="13" t="n">
+        <f aca="false">IF(F12="","",F12*G12)</f>
+        <v>4</v>
+      </c>
+      <c r="I12" s="13" t="str">
+        <f aca="false">IF(F12="","",IF(H12&gt;=15,"Critical",IF(H12&gt;=10,"High",IF(H12&gt;=5,"Medium","Low"))))</f>
+        <v>Low</v>
+      </c>
+      <c r="J12" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="K12" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="L12" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="M12" s="13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="336.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="G12" s="15" t="s">
+      <c r="B13" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C13" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="D13" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="H12" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="I12" s="14" t="s">
-        <v>93</v>
-      </c>
-      <c r="J12" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="K12" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="L12" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="M12" s="14" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="337.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="B13" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="C13" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="D13" s="14" t="s">
-        <v>95</v>
-      </c>
-      <c r="E13" s="14" t="s">
+      <c r="E13" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="F13" s="15" t="s">
+      <c r="F13" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="G13" s="15" t="s">
+      <c r="G13" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="H13" s="14" t="e">
+      <c r="H13" s="13" t="e">
         <f aca="false">IF(F13="","",F13*G13)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="I13" s="14" t="e">
+      <c r="I13" s="13" t="e">
         <f aca="false">IF(F13="","",IF(H13&gt;=15,"Critical",IF(H13&gt;=10,"High",IF(H13&gt;=5,"Medium","Low"))))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J13" s="15" t="s">
+      <c r="J13" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="K13" s="15" t="s">
+      <c r="K13" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="L13" s="14" t="s">
+      <c r="L13" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="M13" s="14" t="s">
+      <c r="M13" s="13" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="337.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="14" t="s">
-        <v>96</v>
-      </c>
-      <c r="B14" s="14" t="s">
+    <row r="14" customFormat="false" ht="336.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="B14" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="C14" s="14" t="s">
+      <c r="C14" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="D14" s="14" t="s">
-        <v>97</v>
-      </c>
-      <c r="E14" s="14" t="s">
-        <v>98</v>
-      </c>
-      <c r="F14" s="15" t="s">
+      <c r="D14" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="F14" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="G14" s="15" t="s">
+      <c r="G14" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="H14" s="14" t="e">
+      <c r="H14" s="13" t="e">
         <f aca="false">IF(F14="","",F14*G14)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="I14" s="14" t="e">
+      <c r="I14" s="13" t="e">
         <f aca="false">IF(F14="","",IF(H14&gt;=15,"Critical",IF(H14&gt;=10,"High",IF(H14&gt;=5,"Medium","Low"))))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J14" s="15" t="s">
+      <c r="J14" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="K14" s="15" t="s">
+      <c r="K14" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="L14" s="14" t="s">
+      <c r="L14" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="M14" s="14" t="s">
+      <c r="M14" s="13" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="270.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="14" t="s">
+    <row r="15" customFormat="false" ht="270" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="F15" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G15" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="H15" s="13" t="n">
+        <f aca="false">IF(F15="","",F15*G15)</f>
+        <v>4</v>
+      </c>
+      <c r="I15" s="13" t="str">
+        <f aca="false">IF(F15="","",IF(H15&gt;=15,"Critical",IF(H15&gt;=10,"High",IF(H15&gt;=5,"Medium","Low"))))</f>
+        <v>Low</v>
+      </c>
+      <c r="J15" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="K15" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="L15" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="M15" s="13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="336.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="B15" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="C15" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="D15" s="14" t="s">
+      <c r="B16" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="D16" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="E15" s="14" t="s">
-        <v>101</v>
-      </c>
-      <c r="F15" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="G15" s="15" t="s">
-        <v>103</v>
-      </c>
-      <c r="H15" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="I15" s="14" t="s">
-        <v>104</v>
-      </c>
-      <c r="J15" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="K15" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="L15" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="M15" s="14" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="337.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="B16" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="C16" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="D16" s="14" t="s">
-        <v>106</v>
-      </c>
-      <c r="E16" s="14" t="s">
+      <c r="E16" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="F16" s="15" t="s">
+      <c r="F16" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="G16" s="15" t="s">
+      <c r="G16" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="H16" s="14" t="e">
+      <c r="H16" s="13" t="e">
         <f aca="false">IF(F16="","",F16*G16)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="I16" s="14" t="e">
+      <c r="I16" s="13" t="e">
         <f aca="false">IF(F16="","",IF(H16&gt;=15,"Critical",IF(H16&gt;=10,"High",IF(H16&gt;=5,"Medium","Low"))))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J16" s="15" t="s">
+      <c r="J16" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="K16" s="15" t="s">
+      <c r="K16" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="L16" s="14" t="s">
+      <c r="L16" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="M16" s="14" t="s">
+      <c r="M16" s="13" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="337.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="14" t="s">
-        <v>107</v>
-      </c>
-      <c r="B17" s="14" t="s">
+    <row r="17" customFormat="false" ht="336.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="B17" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C17" s="14" t="s">
+      <c r="C17" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="D17" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="E17" s="14" t="s">
+      <c r="D17" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="E17" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="F17" s="15" t="s">
+      <c r="F17" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="G17" s="15" t="s">
+      <c r="G17" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="H17" s="14" t="e">
+      <c r="H17" s="13" t="e">
         <f aca="false">IF(F17="","",F17*G17)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="I17" s="14" t="e">
+      <c r="I17" s="13" t="e">
         <f aca="false">IF(F17="","",IF(H17&gt;=15,"Critical",IF(H17&gt;=10,"High",IF(H17&gt;=5,"Medium","Low"))))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J17" s="15" t="s">
+      <c r="J17" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="K17" s="15" t="s">
+      <c r="K17" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="L17" s="14" t="s">
+      <c r="L17" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="M17" s="14" t="s">
+      <c r="M17" s="13" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="337.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="14" t="s">
-        <v>109</v>
-      </c>
-      <c r="B18" s="14" t="s">
+    <row r="18" customFormat="false" ht="336.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="B18" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="C18" s="14" t="s">
+      <c r="C18" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="D18" s="14" t="s">
-        <v>110</v>
-      </c>
-      <c r="E18" s="14" t="s">
+      <c r="D18" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="E18" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="F18" s="15" t="s">
+      <c r="F18" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="G18" s="15" t="s">
+      <c r="G18" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="H18" s="14" t="e">
+      <c r="H18" s="13" t="e">
         <f aca="false">IF(F18="","",F18*G18)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="I18" s="14" t="e">
+      <c r="I18" s="13" t="e">
         <f aca="false">IF(F18="","",IF(H18&gt;=15,"Critical",IF(H18&gt;=10,"High",IF(H18&gt;=5,"Medium","Low"))))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J18" s="15" t="s">
+      <c r="J18" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="K18" s="15" t="s">
+      <c r="K18" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="L18" s="14" t="s">
+      <c r="L18" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="M18" s="14" t="s">
+      <c r="M18" s="13" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="337.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="14" t="s">
-        <v>111</v>
-      </c>
-      <c r="B19" s="14" t="s">
+    <row r="19" customFormat="false" ht="336.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="B19" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="C19" s="14" t="s">
+      <c r="C19" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="D19" s="14" t="s">
-        <v>112</v>
-      </c>
-      <c r="E19" s="14" t="s">
+      <c r="D19" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="E19" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="F19" s="15" t="s">
+      <c r="F19" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="G19" s="15" t="s">
+      <c r="G19" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="H19" s="14" t="e">
+      <c r="H19" s="13" t="e">
         <f aca="false">IF(F19="","",F19*G19)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="I19" s="14" t="e">
+      <c r="I19" s="13" t="e">
         <f aca="false">IF(F19="","",IF(H19&gt;=15,"Critical",IF(H19&gt;=10,"High",IF(H19&gt;=5,"Medium","Low"))))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J19" s="15" t="s">
+      <c r="J19" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="K19" s="15" t="s">
+      <c r="K19" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="L19" s="14" t="s">
+      <c r="L19" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="M19" s="14" t="s">
+      <c r="M19" s="13" t="s">
         <v>67</v>
       </c>
     </row>
@@ -2016,6 +2055,7 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -2025,139 +2065,139 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B19"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="80"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="16" t="s">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="15" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="15" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="11" t="n">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B9" s="16" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="11" t="n">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="B10" s="16" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="11" t="n">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="17" t="s">
+      <c r="B11" s="16" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="11" t="n">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="17" t="s">
+      <c r="B12" s="16" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="11" t="n">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="17" t="s">
+      <c r="B13" s="16" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="16" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="15" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="B9" s="17" t="s">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="10" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="B10" s="17" t="s">
+      <c r="B16" s="16" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="B11" s="17" t="s">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="10" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="B12" s="17" t="s">
+      <c r="B17" s="16" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="B13" s="17" t="s">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="10" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="16" t="s">
+      <c r="B18" s="16" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="11" t="s">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="B16" s="17" t="s">
+      <c r="B19" s="16" t="s">
         <v>127</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="11" t="s">
-        <v>128</v>
-      </c>
-      <c r="B17" s="17" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="11" t="s">
-        <v>130</v>
-      </c>
-      <c r="B18" s="17" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="B19" s="17" t="s">
-        <v>133</v>
       </c>
     </row>
   </sheetData>
@@ -2177,198 +2217,198 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B32"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="50"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="15"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="18" t="s">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="B1" s="17"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="5" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B4" s="1" t="n">
+        <f aca="false">COUNTA('Risk Register'!A2:A16)</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B5" s="1" t="n">
+        <f aca="false">COUNTIF('Risk Register'!I2:I16,"Critical")</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B6" s="1" t="n">
+        <f aca="false">COUNTIF('Risk Register'!I2:I16,"High")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B7" s="1" t="n">
+        <f aca="false">COUNTIF('Risk Register'!I2:I16,"Medium")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B1" s="18"/>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="5" t="s">
+      <c r="B8" s="1" t="n">
+        <f aca="false">COUNTIF('Risk Register'!I2:I16,"Low")</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="B4" s="1" t="n">
-        <f aca="false">COUNTA('Risk Register'!A2:A19)</f>
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
+      <c r="B11" s="1" t="n">
+        <f aca="false">COUNTIF('Risk Register'!C2:C16,"Technical")</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="B5" s="1" t="n">
-        <f aca="false">COUNTIF('Risk Register'!I2:I19,"Critical")</f>
+      <c r="B12" s="1" t="n">
+        <f aca="false">COUNTIF('Risk Register'!C2:C16,"Ethical")</f>
         <v>3</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="B6" s="1" t="n">
-        <f aca="false">COUNTIF('Risk Register'!I2:I19,"High")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
+      <c r="B13" s="1" t="n">
+        <f aca="false">COUNTIF('Risk Register'!C2:C16,"Legal")</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B7" s="1" t="n">
-        <f aca="false">COUNTIF('Risk Register'!I2:I19,"Medium")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="s">
+      <c r="B14" s="1" t="n">
+        <f aca="false">COUNTIF('Risk Register'!C2:C16,"Operational")</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="B8" s="1" t="n">
-        <f aca="false">COUNTIF('Risk Register'!I2:I19,"Low")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="5" t="s">
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="s">
+      <c r="B17" s="1" t="n">
+        <f aca="false">COUNTIF('Risk Register'!B2:B16,"Govern")</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B11" s="1" t="n">
-        <f aca="false">COUNTIF('Risk Register'!C2:C19,"Technical")</f>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="s">
+      <c r="B18" s="1" t="n">
+        <f aca="false">COUNTIF('Risk Register'!B2:B16,"Map")</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="B12" s="1" t="n">
-        <f aca="false">COUNTIF('Risk Register'!C2:C19,"Ethical")</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1" t="s">
+      <c r="B19" s="1" t="n">
+        <f aca="false">COUNTIF('Risk Register'!B2:B16,"Measure")</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B13" s="1" t="n">
-        <f aca="false">COUNTIF('Risk Register'!C2:C19,"Legal")</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="s">
+      <c r="B20" s="1" t="n">
+        <f aca="false">COUNTIF('Risk Register'!B2:B16,"Manage")</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="B14" s="1" t="n">
-        <f aca="false">COUNTIF('Risk Register'!C2:C19,"Operational")</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="5" t="s">
+    </row>
+    <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="18" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="s">
+    <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="18" t="s">
         <v>147</v>
       </c>
-      <c r="B17" s="1" t="n">
-        <f aca="false">COUNTIF('Risk Register'!B2:B19,"Govern")</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1" t="s">
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="B18" s="1" t="n">
-        <f aca="false">COUNTIF('Risk Register'!B2:B19,"Map")</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="1" t="s">
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="B19" s="1" t="n">
-        <f aca="false">COUNTIF('Risk Register'!B2:B19,"Measure")</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="1" t="s">
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="B20" s="1" t="n">
-        <f aca="false">COUNTIF('Risk Register'!B2:B19,"Manage")</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="5" t="s">
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="5" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="19" t="s">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="1" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="19" t="s">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="1" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="1" t="s">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="1" t="s">
         <v>154</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="1" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="1" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="5" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="1" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="1" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="1" t="s">
-        <v>160</v>
       </c>
     </row>
   </sheetData>
@@ -2391,66 +2431,66 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="60"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="70"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="20" t="s">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="19" t="s">
+        <v>155</v>
+      </c>
+      <c r="B1" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="C1" s="19" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>158</v>
+      </c>
+      <c r="C2" s="16" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>160</v>
+      </c>
+      <c r="C3" s="16" t="s">
         <v>161</v>
       </c>
-      <c r="B1" s="20" t="s">
+    </row>
+    <row r="4" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" s="16" t="s">
         <v>162</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="C4" s="16" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="B2" s="17" t="s">
+    <row r="5" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="B5" s="16" t="s">
         <v>164</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="C5" s="16" t="s">
         <v>165</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="17" t="s">
-        <v>78</v>
-      </c>
-      <c r="B3" s="17" t="s">
-        <v>166</v>
-      </c>
-      <c r="C3" s="17" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="B4" s="17" t="s">
-        <v>168</v>
-      </c>
-      <c r="C4" s="17" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="B5" s="17" t="s">
-        <v>170</v>
-      </c>
-      <c r="C5" s="17" t="s">
-        <v>171</v>
       </c>
     </row>
   </sheetData>
